--- a/data/power_curves.xlsx
+++ b/data/power_curves.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanking/Python/era5_gwa_wind_tool/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathanking/Python/era5_gwa_wind_tool/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864F368B-18D2-FF42-A0A3-763D2B778432}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FBC756-A96C-404D-B08C-00BA7071A0D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6780" yWindow="5000" windowWidth="26440" windowHeight="15440" xr2:uid="{2CC13441-AD62-2842-BC7F-AA40F5F25115}"/>
+    <workbookView xWindow="880" yWindow="2120" windowWidth="18720" windowHeight="18260" xr2:uid="{2CC13441-AD62-2842-BC7F-AA40F5F25115}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,27 +25,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Wind Speed (m/s)</t>
   </si>
   <si>
-    <t>GE 164-6.5</t>
+    <t xml:space="preserve">V136-3.6 [1.158kg/m3] </t>
   </si>
   <si>
-    <t>EN-182/7.8</t>
+    <t>V172.7.2 [1.15kg/m3]</t>
   </si>
   <si>
-    <t xml:space="preserve">V136-3.6 [1.158kg/m3] </t>
+    <t>V162.76.2 [1.15kg/m3]</t>
+  </si>
+  <si>
+    <t>EN-182/7.8 [1.225kg/m3]</t>
+  </si>
+  <si>
+    <t>GE 164-6.5 [1.16 kg/m3]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -101,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -114,9 +117,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -436,35 +436,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50720640-EDAD-D243-B6DE-FBC10386C417}">
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" style="4" customWidth="1"/>
     <col min="2" max="4" width="21.1640625" style="5" customWidth="1"/>
-    <col min="5" max="10" width="21.1640625" customWidth="1"/>
+    <col min="5" max="9" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="3" customFormat="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="3" customFormat="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:19" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:18" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>0</v>
       </c>
@@ -474,11 +477,17 @@
       <c r="C2" s="5">
         <v>0</v>
       </c>
-      <c r="D2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2.5</v>
       </c>
@@ -488,297 +497,422 @@
       <c r="C3" s="5">
         <v>0</v>
       </c>
-      <c r="D3" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="5">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="C4" s="5">
         <v>65</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>8.32</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E4" s="5">
+        <v>27</v>
+      </c>
+      <c r="F4" s="5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>3.5</v>
       </c>
       <c r="B5" s="5">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="C5" s="5">
         <v>181</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>74.959999999999994</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E5" s="5">
+        <v>114</v>
+      </c>
+      <c r="F5" s="5">
+        <v>136</v>
+      </c>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>4</v>
       </c>
       <c r="B6" s="5">
-        <v>331</v>
+        <v>290</v>
       </c>
       <c r="C6" s="5">
         <v>340</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>172.6</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E6" s="5">
+        <v>263</v>
+      </c>
+      <c r="F6" s="5">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>4.5</v>
       </c>
       <c r="B7" s="5">
-        <v>506</v>
+        <v>454</v>
       </c>
       <c r="C7" s="5">
         <v>545</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>292.56</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E7" s="5">
+        <v>444</v>
+      </c>
+      <c r="F7" s="5">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="5">
-        <v>721</v>
+        <v>656</v>
       </c>
       <c r="C8" s="5">
         <v>802</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>435.52</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E8" s="5">
+        <v>665</v>
+      </c>
+      <c r="F8" s="5">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>5.5</v>
       </c>
       <c r="B9" s="5">
-        <v>984</v>
+        <v>900</v>
       </c>
       <c r="C9" s="5">
         <v>1105</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>598.48</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E9" s="5">
+        <v>930</v>
+      </c>
+      <c r="F9" s="5">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>1294</v>
+        <v>1191</v>
       </c>
       <c r="C10" s="5">
         <v>1462</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>789.76</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E10" s="5">
+        <v>1250</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>6.5</v>
       </c>
       <c r="B11" s="5">
-        <v>1662</v>
+        <v>1535</v>
       </c>
       <c r="C11" s="5">
         <v>1872</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>1014.36</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E11" s="5">
+        <v>1626</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>7</v>
       </c>
       <c r="B12" s="5">
-        <v>2086</v>
+        <v>1933</v>
       </c>
       <c r="C12" s="5">
         <v>2340</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>1277.28</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E12" s="5">
+        <v>2063</v>
+      </c>
+      <c r="F12" s="5">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>7.5</v>
       </c>
       <c r="B13" s="5">
-        <v>2578</v>
+        <v>2392</v>
       </c>
       <c r="C13" s="5">
         <v>2867</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>1577.2</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E13" s="5">
+        <v>2559</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>8</v>
       </c>
       <c r="B14" s="5">
-        <v>3118</v>
+        <v>2908</v>
       </c>
       <c r="C14" s="5">
         <v>3455</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>1916.12</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E14" s="5">
+        <v>3121</v>
+      </c>
+      <c r="F14" s="5">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>8.5</v>
       </c>
       <c r="B15" s="5">
-        <v>3698</v>
+        <v>3480</v>
       </c>
       <c r="C15" s="5">
         <v>4073</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>2289.7199999999998</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="E15" s="5">
+        <v>3748</v>
+      </c>
+      <c r="F15" s="5">
+        <v>3405</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>9</v>
       </c>
       <c r="B16" s="5">
-        <v>4283</v>
+        <v>4086</v>
       </c>
       <c r="C16" s="5">
         <v>4687</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>2675.68</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16" s="5">
+        <v>4427</v>
+      </c>
+      <c r="F16" s="5">
+        <v>4034</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>9.5</v>
       </c>
       <c r="B17" s="5">
-        <v>4851</v>
+        <v>4695</v>
       </c>
       <c r="C17" s="5">
         <v>5235</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>3026.76</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17" s="5">
+        <v>5058</v>
+      </c>
+      <c r="F17" s="5">
+        <v>4656</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>10</v>
       </c>
       <c r="B18" s="5">
-        <v>5366</v>
+        <v>5264</v>
       </c>
       <c r="C18" s="5">
         <v>5735</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>3314.92</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18" s="5">
+        <v>5643</v>
+      </c>
+      <c r="F18" s="5">
+        <v>5245</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>10.5</v>
       </c>
       <c r="B19" s="5">
-        <v>5797</v>
+        <v>5760</v>
       </c>
       <c r="C19" s="5">
         <v>6212</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>3496.12</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19" s="5">
+        <v>6192</v>
+      </c>
+      <c r="F19" s="5">
+        <v>5714</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>11</v>
       </c>
       <c r="B20" s="5">
-        <v>6120</v>
+        <v>6143</v>
       </c>
       <c r="C20" s="5">
         <v>6607</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>3577.6</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20" s="5">
+        <v>6661</v>
+      </c>
+      <c r="F20" s="5">
+        <v>6036</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>11.5</v>
       </c>
       <c r="B21" s="5">
-        <v>6339</v>
+        <v>6388</v>
       </c>
       <c r="C21" s="5">
         <v>6985</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>3597</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21" s="5">
+        <v>6980</v>
+      </c>
+      <c r="F21" s="5">
+        <v>6151</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>12</v>
       </c>
       <c r="B22" s="5">
-        <v>6446</v>
+        <v>6489</v>
       </c>
       <c r="C22" s="5">
         <v>7282</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22" s="5">
+        <v>7121</v>
+      </c>
+      <c r="F22" s="5">
+        <v>6189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>12.5</v>
       </c>
       <c r="B23" s="5">
-        <v>6499</v>
+        <v>6500</v>
       </c>
       <c r="C23" s="5">
         <v>7516</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23" s="5">
+        <v>7176</v>
+      </c>
+      <c r="F23" s="5">
+        <v>6199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>13</v>
       </c>
@@ -788,11 +922,17 @@
       <c r="C24" s="5">
         <v>7668</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24" s="5">
+        <v>7198</v>
+      </c>
+      <c r="F24" s="5">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>13.5</v>
       </c>
@@ -802,11 +942,17 @@
       <c r="C25" s="5">
         <v>7754</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25" s="5">
+        <v>7199</v>
+      </c>
+      <c r="F25" s="5">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>14</v>
       </c>
@@ -816,11 +962,17 @@
       <c r="C26" s="5">
         <v>7784</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26" s="5">
+        <v>7200</v>
+      </c>
+      <c r="F26" s="5">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>14.5</v>
       </c>
@@ -830,11 +982,17 @@
       <c r="C27" s="5">
         <v>7800</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27" s="5">
+        <v>7200</v>
+      </c>
+      <c r="F27" s="5">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>15</v>
       </c>
@@ -844,11 +1002,17 @@
       <c r="C28" s="5">
         <v>7800</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28" s="5">
+        <v>7200</v>
+      </c>
+      <c r="F28" s="5">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>15.5</v>
       </c>
@@ -858,11 +1022,17 @@
       <c r="C29" s="5">
         <v>7800</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29" s="5">
+        <v>7200</v>
+      </c>
+      <c r="F29" s="5">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>16</v>
       </c>
@@ -872,11 +1042,17 @@
       <c r="C30" s="5">
         <v>7800</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30" s="5">
+        <v>7200</v>
+      </c>
+      <c r="F30" s="5">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>16.5</v>
       </c>
@@ -886,249 +1062,357 @@
       <c r="C31" s="5">
         <v>7800</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31" s="5">
+        <v>7200</v>
+      </c>
+      <c r="F31" s="5">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>17</v>
       </c>
       <c r="B32" s="5">
-        <v>6500</v>
+        <v>6485</v>
       </c>
       <c r="C32" s="5">
         <v>7800</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32" s="5">
+        <v>7200</v>
+      </c>
+      <c r="F32" s="5">
+        <v>6178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>17.5</v>
       </c>
       <c r="B33" s="5">
-        <v>6500</v>
+        <v>6440</v>
       </c>
       <c r="C33" s="5">
         <v>7800</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33" s="5">
+        <v>7190</v>
+      </c>
+      <c r="F33" s="5">
+        <v>6049</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>18</v>
       </c>
       <c r="B34" s="5">
-        <v>6476</v>
+        <v>6369</v>
       </c>
       <c r="C34" s="5">
         <v>7800</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34" s="5">
+        <v>7106</v>
+      </c>
+      <c r="F34" s="5">
+        <v>5813</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>18.5</v>
       </c>
       <c r="B35" s="5">
-        <v>6399</v>
+        <v>6269</v>
       </c>
       <c r="C35" s="5">
         <v>7800</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35" s="5">
+        <v>6935</v>
+      </c>
+      <c r="F35" s="5">
+        <v>5554</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>19</v>
       </c>
       <c r="B36" s="5">
-        <v>6276</v>
+        <v>6128</v>
       </c>
       <c r="C36" s="5">
         <v>7800</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="5">
         <v>3600</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36" s="5">
+        <v>6767</v>
+      </c>
+      <c r="F36" s="5">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>19.5</v>
       </c>
       <c r="B37" s="5">
-        <v>6090</v>
+        <v>5949</v>
       </c>
       <c r="C37" s="5">
         <v>7800</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="5">
         <v>3599</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37" s="5">
+        <v>6607</v>
+      </c>
+      <c r="F37" s="5">
+        <v>5062</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>20</v>
       </c>
       <c r="B38" s="5">
-        <v>5838</v>
+        <v>5705</v>
       </c>
       <c r="C38" s="5">
         <v>7800</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="5">
         <v>3583.64</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38" s="5">
+        <v>6448</v>
+      </c>
+      <c r="F38" s="5">
+        <v>4790</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>20.5</v>
       </c>
       <c r="B39" s="5">
-        <v>5542</v>
+        <v>5435</v>
       </c>
       <c r="C39" s="5">
         <v>7589</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="5">
         <v>3499.92</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39" s="5">
+        <v>6225</v>
+      </c>
+      <c r="F39" s="5">
+        <v>4504</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>21</v>
       </c>
       <c r="B40" s="5">
-        <v>5225</v>
+        <v>5128</v>
       </c>
       <c r="C40" s="5">
         <v>7379</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="5">
         <v>3324.2</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40" s="5">
+        <v>5893</v>
+      </c>
+      <c r="F40" s="5">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>21.5</v>
       </c>
       <c r="B41" s="5">
-        <v>4882</v>
+        <v>4834</v>
       </c>
       <c r="C41" s="5">
         <v>7167</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="5">
         <v>3083.52</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41" s="5">
+        <v>5474</v>
+      </c>
+      <c r="F41" s="5">
+        <v>3928</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>22</v>
       </c>
       <c r="B42" s="5">
-        <v>4535</v>
+        <v>4524</v>
       </c>
       <c r="C42" s="5">
         <v>6954</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="5">
         <v>2827.88</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42" s="5">
+        <v>5011</v>
+      </c>
+      <c r="F42" s="5">
+        <v>3642</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>22.5</v>
       </c>
       <c r="B43" s="5">
-        <v>4185</v>
+        <v>4236</v>
       </c>
       <c r="C43" s="5">
         <v>6743</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="5">
         <v>2580.88</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43" s="5">
+        <v>4538</v>
+      </c>
+      <c r="F43" s="5">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>23</v>
       </c>
       <c r="B44" s="5">
-        <v>3858</v>
+        <v>3960</v>
       </c>
       <c r="C44" s="5">
         <v>6531</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="5">
         <v>2335.2399999999998</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E44" s="5">
+        <v>4064</v>
+      </c>
+      <c r="F44" s="5">
+        <v>3041</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>23.5</v>
       </c>
       <c r="B45" s="5">
-        <v>3639</v>
+        <v>3767</v>
       </c>
       <c r="C45" s="5">
         <v>6319</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="5">
         <v>2085.92</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45" s="5">
+        <v>3586</v>
+      </c>
+      <c r="F45" s="5">
+        <v>2743</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>24</v>
       </c>
       <c r="B46" s="5">
-        <v>3470</v>
+        <v>3604</v>
       </c>
       <c r="C46" s="5">
         <v>6105</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="5">
         <v>1846.6</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46" s="5">
+        <v>3127</v>
+      </c>
+      <c r="F46" s="5">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>24.5</v>
       </c>
       <c r="B47" s="5">
-        <v>3385</v>
+        <v>3484</v>
       </c>
       <c r="C47" s="5">
         <v>5895</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="5">
         <v>1623.28</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47" s="5">
+        <v>2690</v>
+      </c>
+      <c r="F47" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>25</v>
       </c>
       <c r="B48" s="5">
-        <v>3341</v>
+        <v>3416</v>
       </c>
       <c r="C48" s="5">
         <v>5684</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="5">
         <v>1398.28</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48" s="5">
+        <v>2298</v>
+      </c>
+      <c r="F48" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>25.5</v>
       </c>
@@ -1138,11 +1422,17 @@
       <c r="C49" s="5">
         <v>0</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="5">
         <v>1237.96</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E49" s="5">
+        <v>0</v>
+      </c>
+      <c r="F49" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>26</v>
       </c>
@@ -1152,11 +1442,17 @@
       <c r="C50" s="5">
         <v>0</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="5">
         <v>1110.6400000000001</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E50" s="5">
+        <v>0</v>
+      </c>
+      <c r="F50" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>26.5</v>
       </c>
@@ -1166,11 +1462,17 @@
       <c r="C51" s="5">
         <v>0</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="5">
         <v>1057.32</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E51" s="5">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>27</v>
       </c>
@@ -1180,11 +1482,17 @@
       <c r="C52" s="5">
         <v>0</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="5">
         <v>1036</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E52" s="5">
+        <v>0</v>
+      </c>
+      <c r="F52" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>27.5</v>
       </c>
@@ -1194,11 +1502,17 @@
       <c r="C53" s="5">
         <v>0</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="5">
         <v>1035</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E53" s="5">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>28</v>
       </c>
@@ -1208,7 +1522,13 @@
       <c r="C54" s="5">
         <v>0</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="5">
+        <v>0</v>
+      </c>
+      <c r="E54" s="5">
+        <v>0</v>
+      </c>
+      <c r="F54" s="5">
         <v>0</v>
       </c>
     </row>
